--- a/slp/Field_Survey_Template_Kolhapur.xlsx
+++ b/slp/Field_Survey_Template_Kolhapur.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -557,14 +557,14 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GSDA MAHARASHTRA — GROUNDWATER SURVEY &amp; MONITORING MASTER TEMPLATE (KOLHAPUR DISTRICT)</t>
+          <t>GSDA MAHARASHTRA - GROUNDWATER SURVEY &amp; MONITORING MASTER TEMPLATE (OFFICIAL MASTER DISTRICT)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Fill survey records from Row 4 downwards. 'Well No' is the unique sequential well number (e.g. 01). 'Gat No' can be left blank (auto-calculated from GPS LatLong). Dedicated separate columns are provided for Winter and Summer recuperation, individual crops, and 5-layer basalt lithology.</t>
+          <t>INSTRUCTIONS: Fill survey records from Row 4 downwards. 'Well No' is the unique sequential well number (e.g. 01). 'Form Type (Irrigation/PWS)' specifies Irrigation or PWS scheme. 'Mapsheetno' is 10K sheet code (e.g. E43Q02Q). 'Toposheet No.' is SOI 50K Sheet (e.g. 56 C/02). Dedicated separate columns are provided for Winter and Summer recuperation, individual crops, DwL, Curbing (m), Year of Construction, and 5-layer basalt lithology.</t>
         </is>
       </c>
     </row>
@@ -606,265 +606,275 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>Form Type (Irrigation/PWS)</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>Type of well</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Well Owner</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Taluka Name</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Village Name</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>LatLong</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Altitude</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Measuring Point</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Parapet (m)</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>Diameter (m)</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t>effec. Dia</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Curbing (m)</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>Type of curbing</t>
         </is>
       </c>
-      <c r="V3" s="3" t="inlineStr">
+      <c r="W3" s="3" t="inlineStr">
         <is>
           <t>Year of Construction</t>
         </is>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>DwL</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>Winter (SWL)</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="Z3" s="3" t="inlineStr">
         <is>
           <t>Summer (SWL)</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>Type of Pump</t>
         </is>
       </c>
-      <c r="AA3" s="3" t="inlineStr">
+      <c r="AB3" s="3" t="inlineStr">
         <is>
           <t>Mode of Power</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr">
+      <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AD3" s="3" t="inlineStr">
         <is>
           <t>Winter pumping hrs</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
+      <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>Summer pumping hrs</t>
         </is>
       </c>
-      <c r="AE3" s="3" t="inlineStr">
+      <c r="AF3" s="3" t="inlineStr">
         <is>
           <t>winter T req recuperation</t>
         </is>
       </c>
-      <c r="AF3" s="3" t="inlineStr">
+      <c r="AG3" s="3" t="inlineStr">
         <is>
           <t>Summer T req recuperation</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AH3" s="3" t="inlineStr">
         <is>
           <t>Project Irri(PT/MInor)</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>Distance</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>Distance c</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>Cultivable land (Ha)</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>Kharif Crop 1</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t>Kharif Area 1 (Ha)</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>Kharif Crop 2</t>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>Kharif Area 2 (Ha)</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AQ3" s="3" t="inlineStr">
         <is>
           <t>Rabi Crop 1</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AR3" s="3" t="inlineStr">
         <is>
           <t>Rabi Area 1 (Ha)</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>Rabi Crop 2</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
         <is>
           <t>Rabi Area 2 (Ha)</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Perennial Crop</t>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>Perennial Area (Ha)</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>Summer Crop</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Summer Area (Ha)</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AY3" s="3" t="inlineStr">
         <is>
           <t>Lithology 1</t>
         </is>
       </c>
-      <c r="AY3" s="3" t="inlineStr">
+      <c r="AZ3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 1 (m)</t>
         </is>
       </c>
-      <c r="AZ3" s="3" t="inlineStr">
+      <c r="BA3" s="3" t="inlineStr">
         <is>
           <t>Lithology 2</t>
         </is>
       </c>
-      <c r="BA3" s="3" t="inlineStr">
+      <c r="BB3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 2 (m)</t>
         </is>
       </c>
-      <c r="BB3" s="3" t="inlineStr">
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>Lithology 3</t>
         </is>
       </c>
-      <c r="BC3" s="3" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 3 (m)</t>
         </is>
       </c>
-      <c r="BD3" s="3" t="inlineStr">
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>Lithology 4</t>
         </is>
       </c>
-      <c r="BE3" s="3" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 4 (m)</t>
         </is>
       </c>
-      <c r="BF3" s="3" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>Lithology 5</t>
         </is>
       </c>
-      <c r="BG3" s="3" t="inlineStr">
+      <c r="BH3" s="3" t="inlineStr">
         <is>
           <t>Litho Depth 5 (m)</t>
         </is>
       </c>
-      <c r="BH3" s="3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>Toposheet No.</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>Well_Remarks</t>
         </is>
@@ -886,12 +896,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>P. R. Shinde</t>
+          <t>V. N. Nimbalkar</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>E43K04L</t>
+          <t>E43Q02Q</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -902,207 +912,223 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
+          <t>Irrigation</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
           <t>Dug Well</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Sanjay Patil</t>
-        </is>
-      </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Karvir</t>
+          <t>Dhanabai Rathod</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Karvir Rural</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>4200</v>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>16.705000, 74.243300</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>545</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+          <t>South Solapur</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Akkalkot Rural</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>2450</v>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>17.477739, 76.170122</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>465</v>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Top of Parapet</t>
         </is>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="Q4" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="R4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Masonry</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>2018</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>Submersible</t>
+        </is>
+      </c>
+      <c r="AB4" s="4" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG4" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH4" s="4" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="AI4" s="5" t="inlineStr">
+        <is>
+          <t>500m</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
+        <is>
+          <t>Canal</t>
+        </is>
+      </c>
+      <c r="AK4" s="4" t="inlineStr">
+        <is>
+          <t>1km</t>
+        </is>
+      </c>
+      <c r="AL4" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM4" s="4" t="inlineStr">
+        <is>
+          <t>Cotton</t>
+        </is>
+      </c>
+      <c r="AN4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AO4" s="4" t="inlineStr">
+        <is>
+          <t>Soybean</t>
+        </is>
+      </c>
+      <c r="AP4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ4" s="4" t="inlineStr">
+        <is>
+          <t>Wheat</t>
+        </is>
+      </c>
+      <c r="AR4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>Gram</t>
+        </is>
+      </c>
+      <c r="AT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AV4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AX4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" s="4" t="inlineStr">
+        <is>
+          <t>Soil</t>
+        </is>
+      </c>
+      <c r="AZ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA4" s="4" t="inlineStr">
+        <is>
+          <t>Highly Weathered Basalt</t>
+        </is>
+      </c>
+      <c r="BB4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" s="4" t="inlineStr">
+        <is>
+          <t>Moderately Weathered Basalt</t>
+        </is>
+      </c>
+      <c r="BD4" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="R4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="S4" s="4" t="n">
+      <c r="BE4" s="4" t="inlineStr">
+        <is>
+          <t>Fractured/ Jointed Basalt</t>
+        </is>
+      </c>
+      <c r="BF4" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="T4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>Masonry</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>2015</v>
-      </c>
-      <c r="W4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="X4" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="5" t="inlineStr">
-        <is>
-          <t>Submersible</t>
-        </is>
-      </c>
-      <c r="AA4" s="5" t="inlineStr">
-        <is>
-          <t>Electric</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC4" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE4" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG4" s="5" t="inlineStr">
-        <is>
-          <t>Panchganga Project</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="AI4" s="5" t="inlineStr">
-        <is>
-          <t>Left Bank Canal</t>
-        </is>
-      </c>
-      <c r="AJ4" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK4" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL4" s="5" t="inlineStr">
-        <is>
-          <t>Soybean</t>
-        </is>
-      </c>
-      <c r="AM4" s="4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AN4" s="5" t="inlineStr">
-        <is>
-          <t>Paddy</t>
-        </is>
-      </c>
-      <c r="AO4" s="4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP4" s="5" t="inlineStr">
-        <is>
-          <t>Wheat</t>
-        </is>
-      </c>
-      <c r="AQ4" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AR4" s="5" t="inlineStr">
-        <is>
-          <t>Jowar</t>
-        </is>
-      </c>
-      <c r="AS4" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AT4" s="5" t="inlineStr">
-        <is>
-          <t>Sugarcane</t>
-        </is>
-      </c>
-      <c r="AU4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" s="5" t="inlineStr">
-        <is>
-          <t>Groundnut</t>
-        </is>
-      </c>
-      <c r="AW4" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AX4" s="5" t="inlineStr">
-        <is>
-          <t>Lateritic Soil</t>
-        </is>
-      </c>
-      <c r="AY4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" s="5" t="inlineStr">
-        <is>
-          <t>Weathered Basalt</t>
-        </is>
-      </c>
-      <c r="BA4" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB4" s="5" t="inlineStr">
-        <is>
-          <t>Moderately Weathered Basalt</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD4" s="5" t="inlineStr">
-        <is>
-          <t>Jointed Basalt</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF4" s="5" t="inlineStr">
-        <is>
-          <t>Hard Basalt</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="n">
-        <v>12</v>
+      <c r="BG4" s="4" t="inlineStr">
+        <is>
+          <t>Massive Basalt</t>
+        </is>
       </c>
       <c r="BH4" s="5" t="inlineStr">
         <is>
-          <t>High yielding perennial source</t>
+          <t>Bottom</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>56 C/02</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Seasonal yield</t>
         </is>
       </c>
     </row>
